--- a/phosphorus_key.xlsx
+++ b/phosphorus_key.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Phosphorus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87B7FCFB-C719-664E-864E-98B910EFD0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAFB38C-E090-154D-93C7-B7806C337F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{F5821CE9-1002-C040-89B1-4BF40212A527}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="06262026" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,6 +36,89 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="26">
+  <si>
+    <t>Vial Number</t>
+  </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>heron-map_06212026</t>
+  </si>
+  <si>
+    <t>heron-resi_06212026</t>
+  </si>
+  <si>
+    <t>heron-out_06212026</t>
+  </si>
+  <si>
+    <t>elm-school_06212026</t>
+  </si>
+  <si>
+    <t>elm-bridge_06212026</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>gcp_06212026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_06212026</t>
+  </si>
+  <si>
+    <t>adams-in_06212026</t>
+  </si>
+  <si>
+    <t>adams-out_06212026</t>
+  </si>
+  <si>
+    <t>adams-mid-up_06212026</t>
+  </si>
+  <si>
+    <t>gcp_06192026</t>
+  </si>
+  <si>
+    <t>elm-bridge_06192026</t>
+  </si>
+  <si>
+    <t>elm-school_06192026</t>
+  </si>
+  <si>
+    <t>adams-in_06192026</t>
+  </si>
+  <si>
+    <t>adams-mid-up_06192026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_06192026</t>
+  </si>
+  <si>
+    <t>adams-out_06192026</t>
+  </si>
+  <si>
+    <t>heron-resi_06192026</t>
+  </si>
+  <si>
+    <t>heron-map_06192026</t>
+  </si>
+  <si>
+    <t>heron-out_06192026</t>
+  </si>
+  <si>
+    <t>heron-resi_06122026</t>
+  </si>
+  <si>
+    <t>heron-map_06122026</t>
+  </si>
+  <si>
+    <t>heron-out_06122026</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,9 +488,783 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181B7619-D2A8-824A-8E16-6869FF90FC77}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>51</v>
+      </c>
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>52</v>
+      </c>
+      <c r="B45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>53</v>
+      </c>
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>54</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>55</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>56</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>57</v>
+      </c>
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>60</v>
+      </c>
+      <c r="B53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>61</v>
+      </c>
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>62</v>
+      </c>
+      <c r="B55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>63</v>
+      </c>
+      <c r="B56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>64</v>
+      </c>
+      <c r="B57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>65</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>66</v>
+      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>67</v>
+      </c>
+      <c r="B60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>68</v>
+      </c>
+      <c r="B61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>69</v>
+      </c>
+      <c r="B62" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>70</v>
+      </c>
+      <c r="B63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>71</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>72</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>73</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>74</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>75</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>76</v>
+      </c>
+      <c r="B69" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>77</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/phosphorus_key.xlsx
+++ b/phosphorus_key.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaedonswanson/Desktop/School/MS/Research/Phosphorus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAFB38C-E090-154D-93C7-B7806C337F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4308FA7-BB71-AE46-84C3-59D2FF8FEA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{F5821CE9-1002-C040-89B1-4BF40212A527}"/>
+    <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{F5821CE9-1002-C040-89B1-4BF40212A527}"/>
   </bookViews>
   <sheets>
     <sheet name="06262026" sheetId="1" r:id="rId1"/>
+    <sheet name="07242026" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="61">
   <si>
     <t>Vial Number</t>
   </si>
@@ -117,16 +118,127 @@
   </si>
   <si>
     <t>heron-out_06122026</t>
+  </si>
+  <si>
+    <t>gcp_05222026</t>
+  </si>
+  <si>
+    <t>gcp_06122026</t>
+  </si>
+  <si>
+    <t>elm-school_0522026</t>
+  </si>
+  <si>
+    <t>elm-bridge_0522026</t>
+  </si>
+  <si>
+    <t>elm-school_06122026</t>
+  </si>
+  <si>
+    <t>elm-bridge_06122026</t>
+  </si>
+  <si>
+    <t>elm-school_06012026</t>
+  </si>
+  <si>
+    <t>elm-bridge_06112026</t>
+  </si>
+  <si>
+    <t>adams-out_06012026</t>
+  </si>
+  <si>
+    <t>adams-in_06022026</t>
+  </si>
+  <si>
+    <t>adams-out_06122026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_06122026</t>
+  </si>
+  <si>
+    <t>adams-in_06122026</t>
+  </si>
+  <si>
+    <t>gcp_06172026</t>
+  </si>
+  <si>
+    <t>heron-resi_05282026</t>
+  </si>
+  <si>
+    <t>heron-out_05282026</t>
+  </si>
+  <si>
+    <t>adams-in_06172026</t>
+  </si>
+  <si>
+    <t>adams-mid-down_06172026</t>
+  </si>
+  <si>
+    <t>adams-out_06172026</t>
+  </si>
+  <si>
+    <t>elm-school_06172026</t>
+  </si>
+  <si>
+    <t>elm-bridge_06172026</t>
+  </si>
+  <si>
+    <t>heron-resi_06172026</t>
+  </si>
+  <si>
+    <t>heron-map_06172026</t>
+  </si>
+  <si>
+    <t>heron-out_06172026</t>
+  </si>
+  <si>
+    <t>b0</t>
+  </si>
+  <si>
+    <t>b1</t>
+  </si>
+  <si>
+    <t>b2</t>
+  </si>
+  <si>
+    <t>b3</t>
+  </si>
+  <si>
+    <t>p1</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>p3</t>
+  </si>
+  <si>
+    <t>p4</t>
+  </si>
+  <si>
+    <t>p5</t>
+  </si>
+  <si>
+    <t>p6</t>
+  </si>
+  <si>
+    <t>p7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1267,4 +1379,942 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46D2361-45EA-4746-8A4B-18AFB35C8938}">
+  <dimension ref="A1:C84"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>31</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>34</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>35</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>42</v>
+      </c>
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>43</v>
+      </c>
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>45</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>47</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>48</v>
+      </c>
+      <c r="B42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>49</v>
+      </c>
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>50</v>
+      </c>
+      <c r="B44" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>51</v>
+      </c>
+      <c r="B45" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>52</v>
+      </c>
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>53</v>
+      </c>
+      <c r="B47" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>54</v>
+      </c>
+      <c r="B48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>55</v>
+      </c>
+      <c r="B49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>56</v>
+      </c>
+      <c r="B50" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>57</v>
+      </c>
+      <c r="B51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>59</v>
+      </c>
+      <c r="B53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>60</v>
+      </c>
+      <c r="B54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>61</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>62</v>
+      </c>
+      <c r="B56" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>65</v>
+      </c>
+      <c r="B59" t="s">
+        <v>45</v>
+      </c>
+      <c r="C59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>66</v>
+      </c>
+      <c r="B60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>67</v>
+      </c>
+      <c r="B61" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>68</v>
+      </c>
+      <c r="B62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>69</v>
+      </c>
+      <c r="B63" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>70</v>
+      </c>
+      <c r="B64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>71</v>
+      </c>
+      <c r="B65" t="s">
+        <v>47</v>
+      </c>
+      <c r="C65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>72</v>
+      </c>
+      <c r="B66" t="s">
+        <v>47</v>
+      </c>
+      <c r="C66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>73</v>
+      </c>
+      <c r="B67" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>74</v>
+      </c>
+      <c r="B68" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>75</v>
+      </c>
+      <c r="B69" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>76</v>
+      </c>
+      <c r="B70" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>77</v>
+      </c>
+      <c r="B71" t="s">
+        <v>49</v>
+      </c>
+      <c r="C71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>78</v>
+      </c>
+      <c r="B72" t="s">
+        <v>49</v>
+      </c>
+      <c r="C72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>79</v>
+      </c>
+      <c r="B73" t="s">
+        <v>49</v>
+      </c>
+      <c r="C73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>80</v>
+      </c>
+      <c r="B74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>81</v>
+      </c>
+      <c r="B75" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>83</v>
+      </c>
+      <c r="B77" t="s">
+        <v>53</v>
+      </c>
+      <c r="C77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>84</v>
+      </c>
+      <c r="B78" t="s">
+        <v>54</v>
+      </c>
+      <c r="C78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>85</v>
+      </c>
+      <c r="B79" t="s">
+        <v>55</v>
+      </c>
+      <c r="C79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>86</v>
+      </c>
+      <c r="B80" t="s">
+        <v>56</v>
+      </c>
+      <c r="C80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>87</v>
+      </c>
+      <c r="B81" t="s">
+        <v>57</v>
+      </c>
+      <c r="C81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>88</v>
+      </c>
+      <c r="B82" t="s">
+        <v>58</v>
+      </c>
+      <c r="C82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>89</v>
+      </c>
+      <c r="B83" t="s">
+        <v>59</v>
+      </c>
+      <c r="C83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>90</v>
+      </c>
+      <c r="B84" t="s">
+        <v>60</v>
+      </c>
+      <c r="C84">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>